--- a/Feature_Tracker.xlsx
+++ b/Feature_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdoan\source\repos\DEV2-Prototype-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8256AF-B4BC-41BC-ADE9-F9B479FEDA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B292DDB3-88F3-44EB-8898-75112DEBDCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
+    <workbookView xWindow="7620" yWindow="2940" windowWidth="28800" windowHeight="15345" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature Tracker" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
   <si>
     <t>Features</t>
   </si>
@@ -263,6 +263,12 @@
   </si>
   <si>
     <t>Map Layout</t>
+  </si>
+  <si>
+    <t>Burgy</t>
+  </si>
+  <si>
+    <t>Mini Map/ Map System</t>
   </si>
 </sst>
 </file>
@@ -658,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B31B0D-26DC-4CBE-BC71-3F6E3D838FDE}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
@@ -694,6 +700,9 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -844,6 +853,20 @@
       </c>
       <c r="B16" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Feature_Tracker.xlsx
+++ b/Feature_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdoan\source\repos\DEV2-Prototype-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\FullSailAssignments\MidtermLOL\PorjectFolder\DEV2-Prototype-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B292DDB3-88F3-44EB-8898-75112DEBDCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D385AEF-430E-4B2B-9426-C8A5222BA654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="2940" windowWidth="28800" windowHeight="15345" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
+    <workbookView xWindow="0" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature Tracker" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
   <si>
     <t>Features</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>Mini Map/ Map System</t>
+  </si>
+  <si>
+    <t>Pause Menu</t>
+  </si>
+  <si>
+    <t>Working</t>
+  </si>
+  <si>
+    <t>Diego</t>
   </si>
 </sst>
 </file>
@@ -664,16 +673,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B31B0D-26DC-4CBE-BC71-3F6E3D838FDE}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -704,7 +713,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -715,7 +724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -726,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -737,7 +746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -748,7 +757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -759,7 +768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -770,7 +779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -781,7 +790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -792,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -803,7 +812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -814,7 +823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -825,7 +834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -836,7 +845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -847,7 +856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -858,7 +867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -867,6 +876,20 @@
       </c>
       <c r="D17" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -877,16 +900,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C398FDE-FCC4-4A88-B11A-BA70A1CF867C}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -912,7 +935,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -940,14 +963,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0081A6CF-F071-44A0-AF07-8CAC4DF3368E}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="3" max="3" width="25.1796875" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -967,7 +990,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -987,7 +1010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -995,7 +1018,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1011,14 +1034,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E23188-2012-4146-9D07-FBE37AADC30A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -1029,7 +1052,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1040,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -1051,7 +1074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1070,17 +1093,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DBA68-E012-4071-BB01-40F6B88761DB}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="6" max="6" width="23.54296875" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1106,7 +1129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1132,7 +1155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1158,7 +1181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1192,19 +1215,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E254DA5D-0B6B-43EC-A1F5-CFEAA660C151}">
   <dimension ref="A2:L5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="51.28515625" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="39.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" customWidth="1"/>
+    <col min="6" max="6" width="51.26953125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.28515625" customWidth="1"/>
-    <col min="12" max="12" width="71.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.7265625" customWidth="1"/>
+    <col min="11" max="11" width="20.26953125" customWidth="1"/>
+    <col min="12" max="12" width="71.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1230,7 +1253,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>60</v>
       </c>
@@ -1244,7 +1267,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>61</v>
       </c>
@@ -1252,7 +1275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>62</v>
       </c>

--- a/Feature_Tracker.xlsx
+++ b/Feature_Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\FullSailAssignments\MidtermLOL\PorjectFolder\DEV2-Prototype-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdoan\source\repos\DEV2-Prototype-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D385AEF-430E-4B2B-9426-C8A5222BA654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095E029A-2BEF-47C1-87A1-DA47546879B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
+    <workbookView xWindow="-30000" yWindow="3045" windowWidth="28800" windowHeight="15345" xr2:uid="{3D09B86F-DC8E-4082-B780-5053E8B91B87}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature Tracker" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>Features</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Diego</t>
+  </si>
+  <si>
+    <t>Complete</t>
   </si>
 </sst>
 </file>
@@ -674,15 +677,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B31B0D-26DC-4CBE-BC71-3F6E3D838FDE}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="5" max="5" width="11.26953125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -707,13 +710,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -724,7 +727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -735,7 +738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -746,7 +749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -757,7 +760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -768,7 +771,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -779,7 +782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -790,7 +793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -801,7 +804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -812,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -823,7 +826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -834,7 +837,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -845,7 +848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -856,7 +859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -867,7 +870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -878,7 +881,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -900,16 +903,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C398FDE-FCC4-4A88-B11A-BA70A1CF867C}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24.453125" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" customWidth="1"/>
-    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -935,7 +938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -963,14 +966,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0081A6CF-F071-44A0-AF07-8CAC4DF3368E}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="3" max="3" width="25.1796875" customWidth="1"/>
-    <col min="4" max="4" width="20.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -990,7 +993,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1010,7 +1013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1034,14 +1037,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E23188-2012-4146-9D07-FBE37AADC30A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1093,17 +1096,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DBA68-E012-4071-BB01-40F6B88761DB}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
-    <col min="6" max="6" width="23.54296875" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1181,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -1215,19 +1218,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E254DA5D-0B6B-43EC-A1F5-CFEAA660C151}">
   <dimension ref="A2:L5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="39.453125" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" customWidth="1"/>
-    <col min="6" max="6" width="51.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="20.7265625" customWidth="1"/>
-    <col min="11" max="11" width="20.26953125" customWidth="1"/>
-    <col min="12" max="12" width="71.453125" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="71.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>60</v>
       </c>
@@ -1267,7 +1270,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>61</v>
       </c>
@@ -1275,7 +1278,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>62</v>
       </c>
